--- a/experiment/ELAN_bestx8/Test/results-Set14/Set14.xlsx
+++ b/experiment/ELAN_bestx8/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.28</v>
+        <v>21.64</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3166</v>
+        <v>0.3712</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.4</v>
+        <v>24.39</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.6421</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.35</v>
+        <v>22.87</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3922</v>
+        <v>0.4377</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.88</v>
+        <v>24.36</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4026</v>
+        <v>0.4392</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.37</v>
+        <v>20.29</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3689</v>
+        <v>0.4634</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28.73</v>
+        <v>30.15</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6385</v>
+        <v>0.7028</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.31</v>
+        <v>23.92</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5349</v>
+        <v>0.6393</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.36</v>
+        <v>30.2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7048</v>
+        <v>0.8501</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26.16</v>
+        <v>28.61</v>
       </c>
       <c r="C10" t="n">
-        <v>0.656</v>
+        <v>0.7742</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23.09</v>
+        <v>24.29</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5103</v>
+        <v>0.5931999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23.31</v>
+        <v>26.37</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7133</v>
+        <v>0.8487</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.53</v>
+        <v>30.36</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6874</v>
+        <v>0.8205</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18.89</v>
+        <v>21.74</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6461</v>
+        <v>0.8247</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.8</v>
+        <v>21.9</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4458</v>
+        <v>0.5622</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23.25</v>
+        <v>25.08</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.6407</v>
       </c>
     </row>
   </sheetData>
